--- a/public/data/contract_service_commitment.xlsx
+++ b/public/data/contract_service_commitment.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1aad1d19-e783-4816-abb0-58731734cfeb</v>
+        <v>4a7f40d6-d8a9-4f9b-b9ba-58a50ff52363</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D2" t="str">
         <v>CTR-001-001</v>
@@ -447,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0d60977d-11e1-49b7-adaf-1165dd28dd34</v>
+        <v>bfd72f38-61b6-477f-8073-c700c2fb025a</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D3" t="str">
         <v>CTR-001-001</v>
@@ -470,200 +470,200 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>090ed362-7af7-445b-893f-864349e78e7f</v>
+        <v>e1f23ab5-a967-4cef-82d5-d0212bbc6e22</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D4" t="str">
-        <v>CTR-002-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="E4" t="str">
-        <v>Operating hours</v>
+        <v>Dedicated aircraft</v>
       </c>
       <c r="F4" t="str">
-        <v>06:00 - 16:30</v>
+        <v>1 DHC-6 Twin Otter</v>
       </c>
       <c r="G4" t="str">
-        <v>Standard daylight hours</v>
+        <v>Charter dedicated asset for WAI</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>7a841860-4eeb-4f7d-8754-b15c77150351</v>
+        <v>9f86ea43-ff12-45ff-b27d-772bffc96f9f</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D5" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="E5" t="str">
-        <v>Dedicated aircraft</v>
+        <v>Operating hours</v>
       </c>
       <c r="F5" t="str">
-        <v>1 DHC-6 Twin Otter</v>
+        <v>06:00 - 16:30</v>
       </c>
       <c r="G5" t="str">
-        <v>Charter dedicated asset</v>
+        <v>Standard daylight hours</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>65127bf2-be20-4ad9-8ffa-434e66f07c8f</v>
+        <v>46b67179-0acf-474c-8146-62d4185b28e5</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D6" t="str">
-        <v>CTR-005-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="E6" t="str">
-        <v>Operating hours</v>
+        <v>Guaranteed seats</v>
       </c>
       <c r="F6" t="str">
-        <v>06:00 - 16:30</v>
+        <v>30 seats/day</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>Peak season</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1328e52a-db91-46ba-b484-1d11b2f1f2d5</v>
+        <v>ddf2f0a6-aa12-4850-8c9e-77b31876ba9f</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D7" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E7" t="str">
-        <v>Operating hours</v>
+        <v>Dedicated aircraft</v>
       </c>
       <c r="F7" t="str">
-        <v>06:00 - 16:30</v>
+        <v>1 DHC-6 Twin Otter</v>
       </c>
       <c r="G7" t="str">
-        <v>Daylight operations only</v>
+        <v>Soneva charter dedicated asset</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3c186004-835f-4ce1-969a-7b94b5848522</v>
+        <v>fb799a65-15bb-4891-b7d5-029b00f77e5b</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D8" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E8" t="str">
-        <v>Guaranteed seats</v>
+        <v>Operating hours</v>
       </c>
       <c r="F8" t="str">
-        <v>50 seats/day</v>
+        <v>06:00 - 16:30</v>
       </c>
       <c r="G8" t="str">
-        <v>Peak season commitment</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>d28533fc-ebad-4abf-927e-9079c037d0cf</v>
+        <v>3f3d480a-40ca-4f31-8db5-5b42e45e1574</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D9" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-002</v>
       </c>
       <c r="E9" t="str">
-        <v>Response time</v>
+        <v>Operating hours</v>
       </c>
       <c r="F9" t="str">
-        <v>2 hours</v>
+        <v>06:00 - 16:30</v>
       </c>
       <c r="G9" t="str">
-        <v>Booking confirmation SLA</v>
+        <v>Daylight operations</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>4e6ed3b2-e8b8-4057-ab81-6f7539325cc8</v>
+        <v>065f0615-ffaf-43b4-80b7-43713741a984</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D10" t="str">
-        <v>CTR-007-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="E10" t="str">
-        <v>Operating hours</v>
+        <v>Dedicated aircraft</v>
       </c>
       <c r="F10" t="str">
-        <v>06:00 - 22:00</v>
+        <v>1 DHC-6 Twin Otter (Premium)</v>
       </c>
       <c r="G10" t="str">
-        <v>Speedboat extended hours</v>
+        <v>Signed charter luxury interior</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>cd88b683-cf02-4912-b6ce-a4bb8080e63f</v>
+        <v>26d94d42-4eb6-451d-acd5-c8148608b542</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D11" t="str">
-        <v>CTR-007-001</v>
+        <v>CTR-005-001</v>
       </c>
       <c r="E11" t="str">
-        <v>Frequency</v>
+        <v>Operating hours</v>
       </c>
       <c r="F11" t="str">
-        <v>Every 30 minutes</v>
+        <v>06:00 - 16:30</v>
       </c>
       <c r="G11" t="str">
-        <v>Peak hours 07:00-10:00, 14:00-17:00</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>5580a2eb-ccab-4e76-b703-7b816a884626</v>
+        <v>a6ed98af-d61b-4ef7-b586-2c113e4d2585</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D12" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-005-002</v>
       </c>
       <c r="E12" t="str">
         <v>Dedicated aircraft</v>
@@ -672,21 +672,21 @@
         <v>1 DHC-6 Twin Otter</v>
       </c>
       <c r="G12" t="str">
-        <v>Charter asset for Anantara</v>
+        <v>Patina charter</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1e751699-3032-468a-b544-4382f53ae8b3</v>
+        <v>a730bbaf-6102-43b9-a2b8-8f95994daa0c</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D13" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E13" t="str">
         <v>Operating hours</v>
@@ -695,67 +695,67 @@
         <v>06:00 - 16:30</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>Daylight operations only</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>c274e24b-09de-4713-afad-8bfe35a554c4</v>
+        <v>e1a67acb-cf65-4e97-b2a6-b826910e9b6d</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D14" t="str">
-        <v>CTR-009-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E14" t="str">
-        <v>Operating hours</v>
+        <v>Guaranteed seats</v>
       </c>
       <c r="F14" t="str">
-        <v>06:00 - 22:00</v>
+        <v>50 seats/day</v>
       </c>
       <c r="G14" t="str">
-        <v>Speedboat schedule</v>
+        <v>Peak season commitment</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>b2ae5951-4c23-4ecd-8870-2b9fecaaee4c</v>
+        <v>6f766952-8f16-47b6-b48e-379da2a00f43</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D15" t="str">
-        <v>CTR-009-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E15" t="str">
-        <v>Frequency</v>
+        <v>Response time</v>
       </c>
       <c r="F15" t="str">
-        <v>Every 45 minutes</v>
+        <v>2 hours</v>
       </c>
       <c r="G15" t="str">
-        <v>Fixed schedule</v>
+        <v>Booking confirmation SLA</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>c94f241c-2849-42fa-bc0f-23ee2d6dfad3</v>
+        <v>03dc7ad3-8328-405d-addc-017a0b6cab0d</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D16" t="str">
-        <v>CTR-010-001</v>
+        <v>CTR-006-002</v>
       </c>
       <c r="E16" t="str">
         <v>Dedicated aircraft</v>
@@ -764,12 +764,265 @@
         <v>1 DHC-6 Twin Otter</v>
       </c>
       <c r="G16" t="str">
+        <v>FS Landaa charter asset</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>85836a9b-7ddd-4cf7-a636-505a60b7dea7</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D17" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Dedicated aircraft</v>
+      </c>
+      <c r="F17" t="str">
+        <v>1 DHC-6 Twin Otter (VIP)</v>
+      </c>
+      <c r="G17" t="str">
+        <v>VIP configured cabin</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>9f8c01e9-c594-4240-ae6c-6bef9f3d07c1</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D18" t="str">
+        <v>CTR-007-001</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Operating hours</v>
+      </c>
+      <c r="F18" t="str">
+        <v>06:00 - 22:00</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Speedboat extended hours</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>531700a7-b062-41a6-a9a8-d16642b216eb</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D19" t="str">
+        <v>CTR-007-001</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Frequency</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Every 30 minutes</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Peak hours 07:00-10:00, 14:00-17:00</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>5a84d718-69f3-49ce-bd81-27684d0ca7f2</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D20" t="str">
+        <v>CTR-007-002</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Operating hours</v>
+      </c>
+      <c r="F20" t="str">
+        <v>06:00 - 16:30</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Seaplane daylight only</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>568e0ef7-a185-4619-b962-7103a5f1c658</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D21" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Dedicated aircraft</v>
+      </c>
+      <c r="F21" t="str">
+        <v>1 DHC-6 Twin Otter</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Charter asset for Anantara</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>28e1e26b-ae82-4e3c-a9a8-2eca20e7fa00</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D22" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Operating hours</v>
+      </c>
+      <c r="F22" t="str">
+        <v>06:00 - 16:30</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>f8cf952b-2326-4bbe-b18e-d1ed8b27c69e</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D23" t="str">
+        <v>CTR-008-002</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Operating hours</v>
+      </c>
+      <c r="F23" t="str">
+        <v>06:00 - 16:30</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Standard seaplane hours</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>b23cffc0-d74e-46fd-9225-9387b86d7c46</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D24" t="str">
+        <v>CTR-009-001</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Operating hours</v>
+      </c>
+      <c r="F24" t="str">
+        <v>06:00 - 22:00</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Speedboat schedule</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>c4a88b2f-4151-443a-a3e3-69e717c96bd8</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C25" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D25" t="str">
+        <v>CTR-009-001</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Frequency</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Every 45 minutes</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Fixed schedule</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>ee31cf57-effb-48f0-9248-4aa9fffafb41</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C26" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D26" t="str">
+        <v>CTR-010-001</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Dedicated aircraft</v>
+      </c>
+      <c r="F26" t="str">
+        <v>1 DHC-6 Twin Otter</v>
+      </c>
+      <c r="G26" t="str">
         <v>Soneva dedicated charter</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>21b5d7ee-eaaf-46b3-b324-db2c341ca055</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C27" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D27" t="str">
+        <v>CTR-010-002</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Operating hours</v>
+      </c>
+      <c r="F27" t="str">
+        <v>06:00 - 16:30</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Standard hours</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G27"/>
   </ignoredErrors>
 </worksheet>
 </file>